--- a/inputs/test_input_template.xlsx
+++ b/inputs/test_input_template.xlsx
@@ -5,16 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="input_constant" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="input_sensitivity" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="project_sites" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="case_definitions" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="multicriteria_data" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="settings" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="input_constant" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="input_sensitivity" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="project_sites" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="case_definitions" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="multicriteria_data" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="342">
   <si>
     <t xml:space="preserve">Tool for optimizing and simulating off- and on-grid electrification solutions</t>
   </si>
@@ -775,34 +775,58 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
+    <t xml:space="preserve">perform_simulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False or True</t>
+  </si>
+  <si>
     <t xml:space="preserve">based_on_case</t>
   </si>
   <si>
-    <t xml:space="preserve">False or True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pv_fixed_capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oem, string (name of base capacity case), None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storage_fixed_capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">genset_fixed_capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oem, string (name of base capacity case), None, peak_demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcc_consumption_fixed_capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcc_feedin_fixed_capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True or False</t>
+    <t xml:space="preserve">capacity_pv_kWp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oem, float, None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_wind_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_storage_kWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">force_charge_from_maingrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discharge_only_when_blackout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_rectifier_ac_dc_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_inverter_dc_ac_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enable_inverter_only_at_backout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_genset_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">genset_with_minimal_loading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number_of_equal_generators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_pcc_consumption_kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity_pcc_feedin_kW</t>
   </si>
   <si>
     <t xml:space="preserve">max_shortage</t>
@@ -814,7 +838,7 @@
     <t xml:space="preserve">stability_constraint</t>
   </si>
   <si>
-    <t xml:space="preserve"> False, share_usage,  share_backup, share_hybrid (recommended)</t>
+    <t xml:space="preserve">False, share_usage,  share_backup, share_hybrid (recommended)</t>
   </si>
   <si>
     <t xml:space="preserve">renewable_constraint</t>
@@ -829,6 +853,9 @@
     <t xml:space="preserve">Value if known, else None</t>
   </si>
   <si>
+    <t xml:space="preserve">evaluation_perspective</t>
+  </si>
+  <si>
     <t xml:space="preserve">diesel_mg</t>
   </si>
   <si>
@@ -841,61 +868,16 @@
     <t xml:space="preserve">pv-wind-storage-diesel-mg</t>
   </si>
   <si>
-    <t xml:space="preserve">perform_simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_pv_kWp</t>
-  </si>
-  <si>
     <t xml:space="preserve">oem</t>
   </si>
   <si>
-    <t xml:space="preserve">capacity_wind_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_storage_kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">force_charge_from_maingrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">discharge_only_when_blackout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_rectifier_ac_dc_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_inverter_dc_ac_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enable_inverter_only_at_backout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_genset_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">genset_with_minimal_loading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">number_of_equal_generators</t>
-  </si>
-  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">capacity_pcc_consumption_kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capacity_pcc_feedin_kW</t>
-  </si>
-  <si>
     <t xml:space="preserve">default</t>
   </si>
   <si>
     <t xml:space="preserve">share_hybrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evaluation_perspective</t>
   </si>
   <si>
     <t xml:space="preserve">AC_system</t>
@@ -1106,11 +1088,11 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YY\ HH:MM"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy\ hh:mm"/>
     <numFmt numFmtId="167" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1159,11 +1141,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1359,67 +1336,71 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1435,7 +1416,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1447,23 +1428,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1471,39 +1452,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1515,7 +1496,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1523,134 +1504,130 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1715,195 +1692,301 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F20"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="1.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="49.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="1.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="7" style="0" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="1.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="49.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="1.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="7" style="1" width="8.54"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="23.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="1"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="6" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="7" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="7" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="7" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="1"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="7" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true"/>
@@ -1912,7 +1995,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -1921,425 +2004,425 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="18.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="4" style="0" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="4" style="1" width="8.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="20" t="n">
         <v>43101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="20"/>
+      <c r="C22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="20"/>
+      <c r="C23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="20"/>
+      <c r="C28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="21"/>
+      <c r="C29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="0" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="12"/>
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="19" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="21"/>
+      <c r="C33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="23"/>
-      <c r="G34" s="23"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="24"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="21"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="21"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="21"/>
+      <c r="C47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="20"/>
+      <c r="C48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="18" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2355,7 +2438,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -2364,1060 +2447,1060 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G95"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="6.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="4" style="0" width="8.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="6.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="6.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="6.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="4" style="1" width="8.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1024" style="1" width="6.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>9.8</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="25" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>820</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>0.33</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="25" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="16" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="16" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="18" t="n">
+      <c r="B40" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="18" t="n">
+      <c r="B41" s="19" t="n">
         <v>200</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B42" s="18" t="n">
+      <c r="B42" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B43" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B44" s="18" t="n">
+      <c r="B44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="18" t="n">
+      <c r="B46" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B47" s="18" t="n">
+      <c r="B47" s="19" t="n">
         <v>0.68</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="18" t="n">
+      <c r="B48" s="19" t="n">
         <v>0.05</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B49" s="18" t="n">
+      <c r="B49" s="19" t="n">
         <v>20000</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="16" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B50" s="18" t="n">
+      <c r="B50" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="18" t="n">
+      <c r="B51" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B52" s="18" t="n">
+      <c r="B52" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="16" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B53" s="18" t="n">
+      <c r="B53" s="19" t="n">
         <v>1250</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="18" t="n">
+      <c r="B54" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="16" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B55" s="18" t="n">
+      <c r="B55" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="18" t="n">
+      <c r="B56" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B57" s="18" t="n">
+      <c r="B57" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B58" s="18" t="n">
+      <c r="B58" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B59" s="18" t="n">
+      <c r="B59" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="18" t="n">
+      <c r="B60" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="10" t="n">
+      <c r="B61" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="10" t="n">
+      <c r="B62" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="25" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B63" s="18" t="n">
+      <c r="B63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="18" t="n">
+      <c r="B64" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B65" s="18" t="n">
+      <c r="B65" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B66" s="18" t="n">
+      <c r="B66" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B67" s="18" t="n">
+      <c r="B67" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="16" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="18" t="n">
+      <c r="B68" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="16" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B69" s="18" t="n">
+      <c r="B69" s="19" t="n">
         <v>250</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B70" s="18" t="n">
+      <c r="B70" s="19" t="n">
         <v>6.75</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="16" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B71" s="18" t="n">
+      <c r="B71" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B72" s="18" t="n">
+      <c r="B72" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B73" s="18" t="n">
+      <c r="B73" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B74" s="28" t="n">
+      <c r="B74" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B75" s="18" t="n">
+      <c r="B75" s="19" t="n">
         <v>0.97</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B76" s="18" t="n">
+      <c r="B76" s="19" t="n">
         <v>0.97</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B77" s="18" t="n">
+      <c r="B77" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B78" s="18" t="n">
+      <c r="B78" s="19" t="n">
         <v>500</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B79" s="18" t="n">
+      <c r="B79" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B80" s="18" t="n">
+      <c r="B80" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="16" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B82" s="18" t="n">
+      <c r="B82" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B83" s="18" t="n">
+      <c r="B83" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B84" s="18" t="n">
+      <c r="B84" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B85" s="18" t="n">
+      <c r="B85" s="19" t="n">
         <v>0.16</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="18" t="n">
+      <c r="B86" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B87" s="18" t="n">
+      <c r="B87" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B88" s="18" t="n">
+      <c r="B88" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="18" t="n">
+      <c r="B89" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="18" t="n">
+      <c r="B90" s="19" t="n">
         <v>1100</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B91" s="18" t="n">
+      <c r="B91" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B92" s="18" t="n">
+      <c r="B92" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B93" s="18" t="n">
+      <c r="B93" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B94" s="10" t="n">
+      <c r="B94" s="11" t="n">
         <v>2.68</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="25" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B95" s="10" t="n">
+      <c r="B95" s="11" t="n">
         <v>0.9</v>
       </c>
-      <c r="C95" s="24" t="s">
+      <c r="C95" s="25" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3428,7 +3511,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -3437,154 +3520,154 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="12.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="20" width="6.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="21" width="12.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="21" width="9.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="21" width="6.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="1" width="8.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
     </row>
     <row r="4" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3599,7 +3682,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -3608,244 +3691,244 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="9.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="20" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="20" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="8.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="20" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="10" style="20" width="6.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="20" width="12.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="20" width="11.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="21" style="20" width="6.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="6.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="21" width="15.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="21" width="14.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="21" width="9.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="21" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="21" width="9.36"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="21" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="10" style="21" width="6.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="21" width="12.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="21" width="11.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="21" style="21" width="6.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1024" style="1" width="6.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="15"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="10"/>
-      <c r="J2" s="15"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="15"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="15"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="15"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I13" s="10"/>
-      <c r="J13" s="15"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="L14" s="16"/>
+      <c r="L14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="21" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3864,7 +3947,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -3873,540 +3956,665 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="20" width="13.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1018" min="5" style="20" width="6.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1019" style="0" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="21" width="13.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="21" width="23.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1018" min="5" style="21" width="6.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1019" style="1" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33"/>
-    </row>
-    <row r="3" customFormat="false" ht="23.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+    <row r="2" customFormat="false" ht="9.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="34"/>
+    </row>
+    <row r="3" customFormat="false" ht="37.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="34"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="35"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
+      <c r="B7" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+    </row>
+    <row r="29" customFormat="false" ht="123" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
+      <c r="B32" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B33" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="s">
+      <c r="B34" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
+      <c r="B35" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
+      <c r="B36" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="B38" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="B39" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-    </row>
-    <row r="17" customFormat="false" ht="123" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="38" t="s">
+      <c r="B45" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" s="38" t="s">
+      <c r="B46" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="E17" s="38" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
+      <c r="B47" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B48" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" s="39" t="s">
+      <c r="C48" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="D48" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="B20" s="39" t="s">
+      <c r="E48" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="B49" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B21" s="39" t="s">
+      <c r="C49" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="D49" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="E49" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="E21" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
+      <c r="F49" s="40"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="B30" s="39" t="s">
+      <c r="B50" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C50" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="D50" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E50" s="42" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="B37" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="F37" s="39"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="B38" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="E38" s="41" t="s">
-        <v>290</v>
-      </c>
-    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -4415,280 +4623,284 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="8.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="0" width="8.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="8.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="8.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="8.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="15" style="1" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="43"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="42"/>
-    </row>
-    <row r="3" customFormat="false" ht="23.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
         <v>292</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B6" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B7" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B8" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-    </row>
-    <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B10" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="44" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B11" s="48" t="n">
+        <v>0.286229538687379</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="48" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-    </row>
-    <row r="8" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+      <c r="B12" s="48" t="n">
+        <v>0.258073109045841</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B13" s="48" t="n">
+        <v>0.23396226376115</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="48" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
+      <c r="B14" s="48" t="n">
+        <v>0.22173508850563</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="50" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
+      <c r="C17" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="E17" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="B11" s="47" t="n">
-        <v>0.286229538687379</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="s">
+      <c r="F17" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="B12" s="47" t="n">
-        <v>0.258073109045841</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
+      <c r="G17" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="B13" s="47" t="n">
-        <v>0.23396226376115</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
+      <c r="H17" s="49" t="s">
         <v>309</v>
       </c>
-      <c r="B14" s="47" t="n">
-        <v>0.22173508850563</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="48" t="s">
+      <c r="I17" s="49" t="s">
         <v>310</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="s">
-        <v>304</v>
-      </c>
-      <c r="B17" s="49" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="53" t="s">
         <v>311</v>
       </c>
-      <c r="C17" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="E17" s="48" t="s">
+      <c r="B18" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="C18" s="55" t="s">
         <v>313</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="D18" s="56" t="n">
+        <v>0.513888888888889</v>
+      </c>
+      <c r="E18" s="57"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="58" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="53"/>
+      <c r="B19" s="59" t="s">
         <v>314</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="C19" s="60" t="s">
         <v>315</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="D19" s="61" t="n">
+        <v>0.486111111111111</v>
+      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="58" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="53" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="52" t="s">
+      <c r="B20" s="54" t="s">
         <v>317</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="C20" s="55" t="s">
         <v>318</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="D20" s="56" t="n">
+        <v>0.259871031746032</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="58" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="53"/>
+      <c r="B21" s="62" t="s">
         <v>319</v>
       </c>
-      <c r="D18" s="55" t="n">
-        <v>0.513888888888889</v>
-      </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="52"/>
-      <c r="B19" s="58" t="s">
+      <c r="C21" s="48" t="s">
         <v>320</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>321</v>
-      </c>
-      <c r="D19" s="60" t="n">
-        <v>0.486111111111111</v>
-      </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>324</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>0.259871031746032</v>
-      </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="52"/>
-      <c r="B21" s="62" t="s">
-        <v>325</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>326</v>
       </c>
       <c r="D21" s="63" t="n">
         <v>0.238492063492063</v>
       </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="61" t="b">
+      <c r="E21" s="57"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="62" t="s">
-        <v>327</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>328</v>
+        <v>321</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>322</v>
       </c>
       <c r="D22" s="63" t="n">
         <v>0.246825396825397</v>
@@ -4705,19 +4917,20 @@
       <c r="H22" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="61" t="b">
+      <c r="I22" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="52"/>
-      <c r="B23" s="58" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>330</v>
-      </c>
-      <c r="D23" s="60" t="n">
+      <c r="A23" s="53"/>
+      <c r="B23" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" s="61" t="n">
         <v>0.254811507936508</v>
       </c>
       <c r="E23" s="64" t="n">
@@ -4732,19 +4945,20 @@
       <c r="H23" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="61" t="b">
+      <c r="I23" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="66" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B24" s="67" t="s">
-        <v>332</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>333</v>
+        <v>326</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>327</v>
       </c>
       <c r="D24" s="63" t="n">
         <v>0.265354437229437</v>
@@ -4761,7 +4975,8 @@
       <c r="H24" s="65" t="n">
         <v>2.17</v>
       </c>
-      <c r="I24" s="61" t="b">
+      <c r="I24" s="58" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="N24" s="68"/>
@@ -4769,19 +4984,20 @@
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="66"/>
       <c r="B25" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>335</v>
+        <v>328</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>329</v>
       </c>
       <c r="D25" s="63" t="n">
         <v>0.3964420995671</v>
       </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="61" t="b">
+      <c r="E25" s="57"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="N25" s="68"/>
@@ -4789,12 +5005,12 @@
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="66"/>
       <c r="B26" s="69" t="s">
-        <v>336</v>
-      </c>
-      <c r="C26" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="D26" s="60" t="n">
+        <v>330</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="61" t="n">
         <v>0.338203463203463</v>
       </c>
       <c r="E26" s="64" t="n">
@@ -4809,22 +5025,23 @@
       <c r="H26" s="65" t="n">
         <v>2.14</v>
       </c>
-      <c r="I26" s="61" t="b">
+      <c r="I26" s="58" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="N26" s="68"/>
     </row>
     <row r="27" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="70" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B27" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="D27" s="55" t="n">
+        <v>333</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>334</v>
+      </c>
+      <c r="D27" s="56" t="n">
         <v>0.255808080808081</v>
       </c>
       <c r="E27" s="64" t="n">
@@ -4839,20 +5056,21 @@
       <c r="H27" s="65" t="n">
         <v>0.44</v>
       </c>
-      <c r="I27" s="61" t="b">
+      <c r="I27" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J27" s="16" t="s">
-        <v>341</v>
+      <c r="J27" s="17" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="70"/>
       <c r="B28" s="67" t="s">
-        <v>342</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>343</v>
+        <v>336</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>337</v>
       </c>
       <c r="D28" s="63" t="n">
         <v>0.383775252525253</v>
@@ -4869,19 +5087,20 @@
       <c r="H28" s="65" t="n">
         <v>1.88</v>
       </c>
-      <c r="I28" s="61" t="b">
+      <c r="I28" s="58" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="70"/>
       <c r="B29" s="69" t="s">
-        <v>344</v>
-      </c>
-      <c r="C29" s="59" t="s">
-        <v>345</v>
-      </c>
-      <c r="D29" s="60" t="n">
+        <v>338</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="D29" s="61" t="n">
         <v>0.360416666666667</v>
       </c>
       <c r="E29" s="64" t="n">
@@ -4896,47 +5115,48 @@
       <c r="H29" s="65" t="n">
         <v>2.63</v>
       </c>
-      <c r="I29" s="61" t="b">
+      <c r="I29" s="58" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="48" t="s">
-        <v>302</v>
-      </c>
-      <c r="B32" s="48"/>
+      <c r="A32" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="B32" s="49"/>
     </row>
     <row r="33" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="48" t="s">
-        <v>346</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>347</v>
+      <c r="A33" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" s="49" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="str">
+      <c r="A34" s="48" t="str">
         <f aca="false">IF(input_sensitivity!A11 = "","",input_sensitivity!A11)</f>
         <v>pv_cost_investment</v>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="48" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="47" t="str">
+      <c r="A35" s="48" t="str">
         <f aca="false">IF(input_sensitivity!A12 = "","",input_sensitivity!A12)</f>
         <v>pv_lifetime</v>
       </c>
-      <c r="B35" s="47" t="n">
+      <c r="B35" s="48" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4958,8 +5178,8 @@
     <mergeCell ref="A32:B32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
